--- a/詳細設計/01A_画面詳細設計書テンプレート.xlsx
+++ b/詳細設計/01A_画面詳細設計書テンプレート.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="R9a178fe833b64390"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="Rf427e4c352b145e0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_画面概要" sheetId="3" r:id="Re72eba32dab0496c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_画面レイアウト" sheetId="4" r:id="Rea0569623c614619"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_画面項目" sheetId="5" r:id="R3b7e35a8359d49fe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_Component_State" sheetId="6" r:id="R1ff32ebe54e549d8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_Event処理" sheetId="7" r:id="Rd72f97e58c0241c2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_API_Mapping" sheetId="8" r:id="R4270dc4ab88c4624"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_Message_例外" sheetId="9" r:id="R1212ab568cd24be6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_単体テスト観点" sheetId="10" r:id="Rd9a5200bb0b6401a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="R83e42513d26b43a5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="Rc0dfaa28821f4452"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_画面概要" sheetId="3" r:id="R6527f6b2a7b940c1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_画面レイアウト" sheetId="4" r:id="R0278e212854647bf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_画面項目" sheetId="5" r:id="Rd70a8b87afb64a15"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_Component_State" sheetId="6" r:id="Rb1fc64cf062748dd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_Event処理" sheetId="7" r:id="R6f8c93cc9b0b4db5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_API_Mapping" sheetId="8" r:id="Rf16100a0699541c0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_Message_例外" sheetId="9" r:id="R5a9bc492d1f240cd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_単体テスト観点" sheetId="10" r:id="R0912c51be9864f43"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -22,6 +22,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:numFmts count="1">
+    <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
+  </x:numFmts>
   <x:fonts count="11">
     <x:font>
       <x:sz val="11"/>
@@ -412,7 +415,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="147">
+  <x:cellXfs count="148">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -850,6 +853,9 @@
     <x:xf numFmtId="0" fontId="4" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -1389,43 +1395,22 @@
       <x:c r="K21" s="2"/>
       <x:c r="L21" s="2"/>
     </x:row>
-    <x:row r="22" ht="66" customHeight="1">
+    <x:row r="22" ht="100" customHeight="1">
       <x:c r="A22" s="58" t="str">
-        <x:v>本ファイルを複製し、基本設計から当該画面に存在する内容だけを設計する。画面主種別と適用機能を基準に、不要なSection、Placeholder、空行、空Blockは削除する。N/Aや「－」を並べず、基本設計にない機能・ITEM・State・Event・API・Testを推測して追加しない。完成後はITEM・VAL・EVT・API・MSG・UTの参照整合、孤立設計、重複記載を確認し、承認版に未管理のTBDを残さない。</x:v>
-      </x:c>
-      <x:c r="B22" s="59" t="str">
-        <x:v>本ファイルを複製し、基本設計から当該画面に存在する内容だけを設計する。画面主種別と適用機能を基準に、不要なSection、Placeholder、空行、空Blockは削除する。N/Aや「－」を並べず、基本設計にない機能・ITEM・State・Event・API・Testを推測して追加しない。完成後はITEM・VAL・EVT・API・MSG・UTの参照整合、孤立設計、重複記載を確認し、承認版に未管理のTBDを残さない。</x:v>
-      </x:c>
-      <x:c r="C22" s="59" t="str">
-        <x:v>本ファイルを複製し、基本設計から当該画面に存在する内容だけを設計する。画面主種別と適用機能を基準に、不要なSection、Placeholder、空行、空Blockは削除する。N/Aや「－」を並べず、基本設計にない機能・ITEM・State・Event・API・Testを推測して追加しない。完成後はITEM・VAL・EVT・API・MSG・UTの参照整合、孤立設計、重複記載を確認し、承認版に未管理のTBDを残さない。</x:v>
-      </x:c>
-      <x:c r="D22" s="59" t="str">
-        <x:v>本ファイルを複製し、基本設計から当該画面に存在する内容だけを設計する。画面主種別と適用機能を基準に、不要なSection、Placeholder、空行、空Blockは削除する。N/Aや「－」を並べず、基本設計にない機能・ITEM・State・Event・API・Testを推測して追加しない。完成後はITEM・VAL・EVT・API・MSG・UTの参照整合、孤立設計、重複記載を確認し、承認版に未管理のTBDを残さない。</x:v>
-      </x:c>
-      <x:c r="E22" s="59" t="str">
-        <x:v>本ファイルを複製し、基本設計から当該画面に存在する内容だけを設計する。画面主種別と適用機能を基準に、不要なSection、Placeholder、空行、空Blockは削除する。N/Aや「－」を並べず、基本設計にない機能・ITEM・State・Event・API・Testを推測して追加しない。完成後はITEM・VAL・EVT・API・MSG・UTの参照整合、孤立設計、重複記載を確認し、承認版に未管理のTBDを残さない。</x:v>
-      </x:c>
-      <x:c r="F22" s="59" t="str">
-        <x:v>本ファイルを複製し、基本設計から当該画面に存在する内容だけを設計する。画面主種別と適用機能を基準に、不要なSection、Placeholder、空行、空Blockは削除する。N/Aや「－」を並べず、基本設計にない機能・ITEM・State・Event・API・Testを推測して追加しない。完成後はITEM・VAL・EVT・API・MSG・UTの参照整合、孤立設計、重複記載を確認し、承認版に未管理のTBDを残さない。</x:v>
-      </x:c>
-      <x:c r="G22" s="59" t="str">
-        <x:v>本ファイルを複製し、基本設計から当該画面に存在する内容だけを設計する。画面主種別と適用機能を基準に、不要なSection、Placeholder、空行、空Blockは削除する。N/Aや「－」を並べず、基本設計にない機能・ITEM・State・Event・API・Testを推測して追加しない。完成後はITEM・VAL・EVT・API・MSG・UTの参照整合、孤立設計、重複記載を確認し、承認版に未管理のTBDを残さない。</x:v>
-      </x:c>
-      <x:c r="H22" s="59" t="str">
-        <x:v>本ファイルを複製し、基本設計から当該画面に存在する内容だけを設計する。画面主種別と適用機能を基準に、不要なSection、Placeholder、空行、空Blockは削除する。N/Aや「－」を並べず、基本設計にない機能・ITEM・State・Event・API・Testを推測して追加しない。完成後はITEM・VAL・EVT・API・MSG・UTの参照整合、孤立設計、重複記載を確認し、承認版に未管理のTBDを残さない。</x:v>
-      </x:c>
-      <x:c r="I22" s="59" t="str">
-        <x:v>本ファイルを複製し、基本設計から当該画面に存在する内容だけを設計する。画面主種別と適用機能を基準に、不要なSection、Placeholder、空行、空Blockは削除する。N/Aや「－」を並べず、基本設計にない機能・ITEM・State・Event・API・Testを推測して追加しない。完成後はITEM・VAL・EVT・API・MSG・UTの参照整合、孤立設計、重複記載を確認し、承認版に未管理のTBDを残さない。</x:v>
-      </x:c>
-      <x:c r="J22" s="59" t="str">
-        <x:v>本ファイルを複製し、基本設計から当該画面に存在する内容だけを設計する。画面主種別と適用機能を基準に、不要なSection、Placeholder、空行、空Blockは削除する。N/Aや「－」を並べず、基本設計にない機能・ITEM・State・Event・API・Testを推測して追加しない。完成後はITEM・VAL・EVT・API・MSG・UTの参照整合、孤立設計、重複記載を確認し、承認版に未管理のTBDを残さない。</x:v>
-      </x:c>
-      <x:c r="K22" s="59" t="str">
-        <x:v>本ファイルを複製し、基本設計から当該画面に存在する内容だけを設計する。画面主種別と適用機能を基準に、不要なSection、Placeholder、空行、空Blockは削除する。N/Aや「－」を並べず、基本設計にない機能・ITEM・State・Event・API・Testを推測して追加しない。完成後はITEM・VAL・EVT・API・MSG・UTの参照整合、孤立設計、重複記載を確認し、承認版に未管理のTBDを残さない。</x:v>
-      </x:c>
-      <x:c r="L22" s="60" t="str">
-        <x:v>本ファイルを複製し、基本設計から当該画面に存在する内容だけを設計する。画面主種別と適用機能を基準に、不要なSection、Placeholder、空行、空Blockは削除する。N/Aや「－」を並べず、基本設計にない機能・ITEM・State・Event・API・Testを推測して追加しない。完成後はITEM・VAL・EVT・API・MSG・UTの参照整合、孤立設計、重複記載を確認し、承認版に未管理のTBDを残さない。</x:v>
-      </x:c>
+        <x:v>文書状態：Review済／承認待ち。二次Review日：2026-09-30。
+本ファイルを複製し、基本設計から当該画面に存在する内容だけを設計する。画面主種別と適用機能を基準に、不要なSection、Placeholder、空行、空Blockは削除する。N/Aや「－」を並べず、基本設計にない機能・ITEM・State・Event・API・Testを推測して追加しない。完成後はITEM・VAL・EVT・API・MSG・UTの参照整合、孤立設計、重複記載を確認し、承認版に未管理のTBDを残さない。</x:v>
+      </x:c>
+      <x:c r="B22" s="59"/>
+      <x:c r="C22" s="59"/>
+      <x:c r="D22" s="59"/>
+      <x:c r="E22" s="59"/>
+      <x:c r="F22" s="59"/>
+      <x:c r="G22" s="59"/>
+      <x:c r="H22" s="59"/>
+      <x:c r="I22" s="59"/>
+      <x:c r="J22" s="59"/>
+      <x:c r="K22" s="59"/>
+      <x:c r="L22" s="60"/>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="61"/>
@@ -3691,30 +3676,30 @@
       <x:c r="K10" s="2"/>
       <x:c r="L10" s="2"/>
     </x:row>
-    <x:row r="11">
+    <x:row r="11" ht="84" customHeight="1">
       <x:c r="A11" s="111" t="str">
-        <x:v>&lt;&lt;Ver.x.x&gt;&gt;</x:v>
-      </x:c>
-      <x:c r="B11" s="111" t="str">
-        <x:v>&lt;&lt;yyyy-mm-dd&gt;&gt;</x:v>
+        <x:v>Ver.2.2</x:v>
+      </x:c>
+      <x:c r="B11" s="147" t="n">
+        <x:v>46295</x:v>
       </x:c>
       <x:c r="C11" s="111" t="str">
-        <x:v>&lt;&lt;新規／改訂／削除&gt;&gt;</x:v>
+        <x:v>Review</x:v>
       </x:c>
       <x:c r="D11" s="111" t="str">
-        <x:v>&lt;&lt;改訂内容&gt;&gt;</x:v>
+        <x:v>二次Review完了。設計内容変更なし。Review済／承認待ちへ整理。</x:v>
       </x:c>
       <x:c r="E11" s="111" t="str">
-        <x:v>&lt;&lt;記入&gt;&gt;</x:v>
+        <x:v>－</x:v>
       </x:c>
       <x:c r="F11" s="111" t="str">
-        <x:v>&lt;&lt;記入&gt;&gt;</x:v>
+        <x:v>Review済</x:v>
       </x:c>
       <x:c r="G11" s="111" t="str">
-        <x:v>&lt;&lt;記入&gt;&gt;</x:v>
+        <x:v>－</x:v>
       </x:c>
       <x:c r="H11" s="111" t="str">
-        <x:v>&lt;&lt;状態&gt;&gt;</x:v>
+        <x:v>承認待ち</x:v>
       </x:c>
       <x:c r="I11" s="2"/>
       <x:c r="J11" s="2"/>

--- a/詳細設計/01A_画面詳細設計書テンプレート.xlsx
+++ b/詳細設計/01A_画面詳細設計書テンプレート.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="R83e42513d26b43a5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="Rc0dfaa28821f4452"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_画面概要" sheetId="3" r:id="R6527f6b2a7b940c1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_画面レイアウト" sheetId="4" r:id="R0278e212854647bf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_画面項目" sheetId="5" r:id="Rd70a8b87afb64a15"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_Component_State" sheetId="6" r:id="Rb1fc64cf062748dd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_Event処理" sheetId="7" r:id="R6f8c93cc9b0b4db5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_API_Mapping" sheetId="8" r:id="Rf16100a0699541c0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_Message_例外" sheetId="9" r:id="R5a9bc492d1f240cd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_単体テスト観点" sheetId="10" r:id="R0912c51be9864f43"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="R9a178fe833b64390"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="Rf427e4c352b145e0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_画面概要" sheetId="3" r:id="Re72eba32dab0496c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_画面レイアウト" sheetId="4" r:id="Rea0569623c614619"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_画面項目" sheetId="5" r:id="R3b7e35a8359d49fe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_Component_State" sheetId="6" r:id="R1ff32ebe54e549d8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_Event処理" sheetId="7" r:id="Rd72f97e58c0241c2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_API_Mapping" sheetId="8" r:id="R4270dc4ab88c4624"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_Message_例外" sheetId="9" r:id="R1212ab568cd24be6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_単体テスト観点" sheetId="10" r:id="Rd9a5200bb0b6401a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -22,9 +22,6 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="1">
-    <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
-  </x:numFmts>
   <x:fonts count="11">
     <x:font>
       <x:sz val="11"/>
@@ -415,7 +412,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="148">
+  <x:cellXfs count="147">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -853,9 +850,6 @@
     <x:xf numFmtId="0" fontId="4" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="200" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -1395,22 +1389,43 @@
       <x:c r="K21" s="2"/>
       <x:c r="L21" s="2"/>
     </x:row>
-    <x:row r="22" ht="100" customHeight="1">
+    <x:row r="22" ht="66" customHeight="1">
       <x:c r="A22" s="58" t="str">
-        <x:v>文書状態：Review済／承認待ち。二次Review日：2026-09-30。
-本ファイルを複製し、基本設計から当該画面に存在する内容だけを設計する。画面主種別と適用機能を基準に、不要なSection、Placeholder、空行、空Blockは削除する。N/Aや「－」を並べず、基本設計にない機能・ITEM・State・Event・API・Testを推測して追加しない。完成後はITEM・VAL・EVT・API・MSG・UTの参照整合、孤立設計、重複記載を確認し、承認版に未管理のTBDを残さない。</x:v>
-      </x:c>
-      <x:c r="B22" s="59"/>
-      <x:c r="C22" s="59"/>
-      <x:c r="D22" s="59"/>
-      <x:c r="E22" s="59"/>
-      <x:c r="F22" s="59"/>
-      <x:c r="G22" s="59"/>
-      <x:c r="H22" s="59"/>
-      <x:c r="I22" s="59"/>
-      <x:c r="J22" s="59"/>
-      <x:c r="K22" s="59"/>
-      <x:c r="L22" s="60"/>
+        <x:v>本ファイルを複製し、基本設計から当該画面に存在する内容だけを設計する。画面主種別と適用機能を基準に、不要なSection、Placeholder、空行、空Blockは削除する。N/Aや「－」を並べず、基本設計にない機能・ITEM・State・Event・API・Testを推測して追加しない。完成後はITEM・VAL・EVT・API・MSG・UTの参照整合、孤立設計、重複記載を確認し、承認版に未管理のTBDを残さない。</x:v>
+      </x:c>
+      <x:c r="B22" s="59" t="str">
+        <x:v>本ファイルを複製し、基本設計から当該画面に存在する内容だけを設計する。画面主種別と適用機能を基準に、不要なSection、Placeholder、空行、空Blockは削除する。N/Aや「－」を並べず、基本設計にない機能・ITEM・State・Event・API・Testを推測して追加しない。完成後はITEM・VAL・EVT・API・MSG・UTの参照整合、孤立設計、重複記載を確認し、承認版に未管理のTBDを残さない。</x:v>
+      </x:c>
+      <x:c r="C22" s="59" t="str">
+        <x:v>本ファイルを複製し、基本設計から当該画面に存在する内容だけを設計する。画面主種別と適用機能を基準に、不要なSection、Placeholder、空行、空Blockは削除する。N/Aや「－」を並べず、基本設計にない機能・ITEM・State・Event・API・Testを推測して追加しない。完成後はITEM・VAL・EVT・API・MSG・UTの参照整合、孤立設計、重複記載を確認し、承認版に未管理のTBDを残さない。</x:v>
+      </x:c>
+      <x:c r="D22" s="59" t="str">
+        <x:v>本ファイルを複製し、基本設計から当該画面に存在する内容だけを設計する。画面主種別と適用機能を基準に、不要なSection、Placeholder、空行、空Blockは削除する。N/Aや「－」を並べず、基本設計にない機能・ITEM・State・Event・API・Testを推測して追加しない。完成後はITEM・VAL・EVT・API・MSG・UTの参照整合、孤立設計、重複記載を確認し、承認版に未管理のTBDを残さない。</x:v>
+      </x:c>
+      <x:c r="E22" s="59" t="str">
+        <x:v>本ファイルを複製し、基本設計から当該画面に存在する内容だけを設計する。画面主種別と適用機能を基準に、不要なSection、Placeholder、空行、空Blockは削除する。N/Aや「－」を並べず、基本設計にない機能・ITEM・State・Event・API・Testを推測して追加しない。完成後はITEM・VAL・EVT・API・MSG・UTの参照整合、孤立設計、重複記載を確認し、承認版に未管理のTBDを残さない。</x:v>
+      </x:c>
+      <x:c r="F22" s="59" t="str">
+        <x:v>本ファイルを複製し、基本設計から当該画面に存在する内容だけを設計する。画面主種別と適用機能を基準に、不要なSection、Placeholder、空行、空Blockは削除する。N/Aや「－」を並べず、基本設計にない機能・ITEM・State・Event・API・Testを推測して追加しない。完成後はITEM・VAL・EVT・API・MSG・UTの参照整合、孤立設計、重複記載を確認し、承認版に未管理のTBDを残さない。</x:v>
+      </x:c>
+      <x:c r="G22" s="59" t="str">
+        <x:v>本ファイルを複製し、基本設計から当該画面に存在する内容だけを設計する。画面主種別と適用機能を基準に、不要なSection、Placeholder、空行、空Blockは削除する。N/Aや「－」を並べず、基本設計にない機能・ITEM・State・Event・API・Testを推測して追加しない。完成後はITEM・VAL・EVT・API・MSG・UTの参照整合、孤立設計、重複記載を確認し、承認版に未管理のTBDを残さない。</x:v>
+      </x:c>
+      <x:c r="H22" s="59" t="str">
+        <x:v>本ファイルを複製し、基本設計から当該画面に存在する内容だけを設計する。画面主種別と適用機能を基準に、不要なSection、Placeholder、空行、空Blockは削除する。N/Aや「－」を並べず、基本設計にない機能・ITEM・State・Event・API・Testを推測して追加しない。完成後はITEM・VAL・EVT・API・MSG・UTの参照整合、孤立設計、重複記載を確認し、承認版に未管理のTBDを残さない。</x:v>
+      </x:c>
+      <x:c r="I22" s="59" t="str">
+        <x:v>本ファイルを複製し、基本設計から当該画面に存在する内容だけを設計する。画面主種別と適用機能を基準に、不要なSection、Placeholder、空行、空Blockは削除する。N/Aや「－」を並べず、基本設計にない機能・ITEM・State・Event・API・Testを推測して追加しない。完成後はITEM・VAL・EVT・API・MSG・UTの参照整合、孤立設計、重複記載を確認し、承認版に未管理のTBDを残さない。</x:v>
+      </x:c>
+      <x:c r="J22" s="59" t="str">
+        <x:v>本ファイルを複製し、基本設計から当該画面に存在する内容だけを設計する。画面主種別と適用機能を基準に、不要なSection、Placeholder、空行、空Blockは削除する。N/Aや「－」を並べず、基本設計にない機能・ITEM・State・Event・API・Testを推測して追加しない。完成後はITEM・VAL・EVT・API・MSG・UTの参照整合、孤立設計、重複記載を確認し、承認版に未管理のTBDを残さない。</x:v>
+      </x:c>
+      <x:c r="K22" s="59" t="str">
+        <x:v>本ファイルを複製し、基本設計から当該画面に存在する内容だけを設計する。画面主種別と適用機能を基準に、不要なSection、Placeholder、空行、空Blockは削除する。N/Aや「－」を並べず、基本設計にない機能・ITEM・State・Event・API・Testを推測して追加しない。完成後はITEM・VAL・EVT・API・MSG・UTの参照整合、孤立設計、重複記載を確認し、承認版に未管理のTBDを残さない。</x:v>
+      </x:c>
+      <x:c r="L22" s="60" t="str">
+        <x:v>本ファイルを複製し、基本設計から当該画面に存在する内容だけを設計する。画面主種別と適用機能を基準に、不要なSection、Placeholder、空行、空Blockは削除する。N/Aや「－」を並べず、基本設計にない機能・ITEM・State・Event・API・Testを推測して追加しない。完成後はITEM・VAL・EVT・API・MSG・UTの参照整合、孤立設計、重複記載を確認し、承認版に未管理のTBDを残さない。</x:v>
+      </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="61"/>
@@ -3676,30 +3691,30 @@
       <x:c r="K10" s="2"/>
       <x:c r="L10" s="2"/>
     </x:row>
-    <x:row r="11" ht="84" customHeight="1">
+    <x:row r="11">
       <x:c r="A11" s="111" t="str">
-        <x:v>Ver.2.2</x:v>
-      </x:c>
-      <x:c r="B11" s="147" t="n">
-        <x:v>46295</x:v>
+        <x:v>&lt;&lt;Ver.x.x&gt;&gt;</x:v>
+      </x:c>
+      <x:c r="B11" s="111" t="str">
+        <x:v>&lt;&lt;yyyy-mm-dd&gt;&gt;</x:v>
       </x:c>
       <x:c r="C11" s="111" t="str">
-        <x:v>Review</x:v>
+        <x:v>&lt;&lt;新規／改訂／削除&gt;&gt;</x:v>
       </x:c>
       <x:c r="D11" s="111" t="str">
-        <x:v>二次Review完了。設計内容変更なし。Review済／承認待ちへ整理。</x:v>
+        <x:v>&lt;&lt;改訂内容&gt;&gt;</x:v>
       </x:c>
       <x:c r="E11" s="111" t="str">
-        <x:v>－</x:v>
+        <x:v>&lt;&lt;記入&gt;&gt;</x:v>
       </x:c>
       <x:c r="F11" s="111" t="str">
-        <x:v>Review済</x:v>
+        <x:v>&lt;&lt;記入&gt;&gt;</x:v>
       </x:c>
       <x:c r="G11" s="111" t="str">
-        <x:v>－</x:v>
+        <x:v>&lt;&lt;記入&gt;&gt;</x:v>
       </x:c>
       <x:c r="H11" s="111" t="str">
-        <x:v>承認待ち</x:v>
+        <x:v>&lt;&lt;状態&gt;&gt;</x:v>
       </x:c>
       <x:c r="I11" s="2"/>
       <x:c r="J11" s="2"/>

--- a/詳細設計/01A_画面詳細設計書テンプレート.xlsx
+++ b/詳細設計/01A_画面詳細設計書テンプレート.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="R83e42513d26b43a5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="Rc0dfaa28821f4452"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_画面概要" sheetId="3" r:id="R6527f6b2a7b940c1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_画面レイアウト" sheetId="4" r:id="R0278e212854647bf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_画面項目" sheetId="5" r:id="Rd70a8b87afb64a15"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_Component_State" sheetId="6" r:id="Rb1fc64cf062748dd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_Event処理" sheetId="7" r:id="R6f8c93cc9b0b4db5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_API_Mapping" sheetId="8" r:id="Rf16100a0699541c0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_Message_例外" sheetId="9" r:id="R5a9bc492d1f240cd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_単体テスト観点" sheetId="10" r:id="R0912c51be9864f43"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="R3245ccdba70d4e80"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="R667751ada7e047ec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_画面概要" sheetId="3" r:id="R9adfd77cb07645c1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_画面レイアウト" sheetId="4" r:id="Rba9b8efcea7b42b6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_画面項目" sheetId="5" r:id="R1e6df2507b714eec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_Component_State" sheetId="6" r:id="R3277bdacec6b422a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_Event処理" sheetId="7" r:id="Rd5a8fe5a62e043a6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_API_Mapping" sheetId="8" r:id="R6a3f4c9dfca6425f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_Message_例外" sheetId="9" r:id="R900b0160efd040d3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_単体テスト観点" sheetId="10" r:id="R5d6cf6ba0ada4665"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -4112,7 +4112,7 @@
         <x:v>&lt;&lt;ファイル／Sheet／行&gt;&gt;</x:v>
       </x:c>
       <x:c r="D10" s="81" t="str">
-        <x:v>成果物一覧と一致</x:v>
+        <x:v>基本設計の画面IDと一致</x:v>
       </x:c>
       <x:c r="E10" s="2"/>
       <x:c r="F10" s="2"/>

--- a/詳細設計/01A_画面詳細設計書テンプレート.xlsx
+++ b/詳細設計/01A_画面詳細設計書テンプレート.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="R3245ccdba70d4e80"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="R667751ada7e047ec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_画面概要" sheetId="3" r:id="R9adfd77cb07645c1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_画面レイアウト" sheetId="4" r:id="Rba9b8efcea7b42b6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_画面項目" sheetId="5" r:id="R1e6df2507b714eec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_Component_State" sheetId="6" r:id="R3277bdacec6b422a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_Event処理" sheetId="7" r:id="Rd5a8fe5a62e043a6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_API_Mapping" sheetId="8" r:id="R6a3f4c9dfca6425f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_Message_例外" sheetId="9" r:id="R900b0160efd040d3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_単体テスト観点" sheetId="10" r:id="R5d6cf6ba0ada4665"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="R5fb8a5f29a5140d5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="R48f27eb794ee4c35"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_画面概要" sheetId="3" r:id="Rc2197414232a4acb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_画面レイアウト" sheetId="4" r:id="Rae125e082dfd49dc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_画面項目" sheetId="5" r:id="R333ee02eb05f47b6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_Component_State" sheetId="6" r:id="Rb83ceb556c2f427b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_Event処理" sheetId="7" r:id="R0a20fe62df3a4b59"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_API_Mapping" sheetId="8" r:id="R2886ea569c54490b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_Message_例外" sheetId="9" r:id="Raa83f0f680d04efe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_単体テスト観点" sheetId="10" r:id="Rde41f8f87dd84472"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1286,7 +1286,7 @@
       <x:c r="D15" s="36"/>
       <x:c r="E15" s="36"/>
       <x:c r="F15" s="38" t="str">
-        <x:v>Ver.2.2</x:v>
+        <x:v>Ver.2.3</x:v>
       </x:c>
       <x:c r="G15" s="38"/>
       <x:c r="H15" s="38"/>
@@ -1397,7 +1397,7 @@
     </x:row>
     <x:row r="22" ht="100" customHeight="1">
       <x:c r="A22" s="58" t="str">
-        <x:v>文書状態：Review済／承認待ち。二次Review日：2026-09-30。
+        <x:v>文書状態：修正済／Review待ち。改訂日：2026-10-15。
 本ファイルを複製し、基本設計から当該画面に存在する内容だけを設計する。画面主種別と適用機能を基準に、不要なSection、Placeholder、空行、空Blockは削除する。N/Aや「－」を並べず、基本設計にない機能・ITEM・State・Event・API・Testを推測して追加しない。完成後はITEM・VAL・EVT・API・MSG・UTの参照整合、孤立設計、重複記載を確認し、承認版に未管理のTBDを残さない。</x:v>
       </x:c>
       <x:c r="B22" s="59"/>
@@ -1597,7 +1597,7 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="J2" s="69" t="str">
-        <x:v>Ver.2.2</x:v>
+        <x:v>Ver.2.3</x:v>
       </x:c>
       <x:c r="K2" s="69"/>
       <x:c r="L2" s="69"/>
@@ -1741,7 +1741,7 @@
         <x:v>期待する遷移</x:v>
       </x:c>
       <x:c r="J9" s="131" t="str">
-        <x:v>Message ID</x:v>
+        <x:v>Message／業務Code</x:v>
       </x:c>
       <x:c r="K9" s="131" t="str">
         <x:v>確認対象／証跡</x:v>
@@ -3493,7 +3493,7 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="J2" s="69" t="str">
-        <x:v>Ver.2.2</x:v>
+        <x:v>Ver.2.3</x:v>
       </x:c>
       <x:c r="K2" s="69"/>
       <x:c r="L2" s="69"/>
@@ -3707,14 +3707,30 @@
       <x:c r="L11" s="2"/>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="2"/>
-      <x:c r="B12" s="2"/>
-      <x:c r="C12" s="2"/>
-      <x:c r="D12" s="2"/>
-      <x:c r="E12" s="2"/>
-      <x:c r="F12" s="2"/>
-      <x:c r="G12" s="2"/>
-      <x:c r="H12" s="2"/>
+      <x:c r="A12" s="111" t="str">
+        <x:v>Ver.2.3</x:v>
+      </x:c>
+      <x:c r="B12" s="147" t="str">
+        <x:v>2026-10-15</x:v>
+      </x:c>
+      <x:c r="C12" s="111" t="str">
+        <x:v>改訂</x:v>
+      </x:c>
+      <x:c r="D12" s="111" t="str">
+        <x:v>State ID列を実成果物と統一し、正本根拠とMessage／業務Codeを明確化。</x:v>
+      </x:c>
+      <x:c r="E12" s="111" t="str">
+        <x:v>Project Leader</x:v>
+      </x:c>
+      <x:c r="F12" s="111" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="G12" s="111" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="H12" s="111" t="str">
+        <x:v>Review待ち</x:v>
+      </x:c>
       <x:c r="I12" s="2"/>
       <x:c r="J12" s="2"/>
       <x:c r="K12" s="2"/>
@@ -3964,7 +3980,7 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="J2" s="69" t="str">
-        <x:v>Ver.2.2</x:v>
+        <x:v>Ver.2.3</x:v>
       </x:c>
       <x:c r="K2" s="69"/>
       <x:c r="L2" s="69"/>
@@ -3999,7 +4015,7 @@
     </x:row>
     <x:row r="5" ht="44" customHeight="1">
       <x:c r="A5" s="58" t="str">
-        <x:v>作成前に基本設計から画面主種別、適用機能、UI項目、操作、API、業務ルール、エラーを抽出する。画面主種別で主要な役割を判断し、適用機能に基づいてEvent・State・API・Message・Testの要否を決める。適用しない機能の行やSectionは最終成果物から削除する。</x:v>
+        <x:v>画面主種別、UI項目、操作、API、業務ルール、Errorを基本設計から抽出し、実装に必要な値・条件・結果を本書に具体的に記載する。根拠は基本設計File名／Sheet名／設計ID又はCell位置で示す。</x:v>
       </x:c>
       <x:c r="B5" s="59" t="str">
         <x:v>作成前に基本設計から画面主種別、適用機能、UI項目、操作、API、業務ルール、エラーを抽出する。画面主種別で主要な役割を判断し、適用機能に基づいてEvent・State・API・Message・Testの要否を決める。適用しない機能の行やSectionは最終成果物から削除する。</x:v>
@@ -5119,7 +5135,7 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="J2" s="69" t="str">
-        <x:v>Ver.2.2</x:v>
+        <x:v>Ver.2.3</x:v>
       </x:c>
       <x:c r="K2" s="69"/>
       <x:c r="L2" s="69"/>
@@ -6581,7 +6597,7 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="J2" s="69" t="str">
-        <x:v>Ver.2.2</x:v>
+        <x:v>Ver.2.3</x:v>
       </x:c>
       <x:c r="K2" s="69"/>
       <x:c r="L2" s="69"/>
@@ -8527,7 +8543,7 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="J2" s="69" t="str">
-        <x:v>Ver.2.2</x:v>
+        <x:v>Ver.2.3</x:v>
       </x:c>
       <x:c r="K2" s="69"/>
       <x:c r="L2" s="69"/>
@@ -8562,7 +8578,7 @@
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="58" t="str">
-        <x:v>実際に存在し、実装理解に必要なComponentとStateだけを記載する。表を埋めるための分割や、存在しないDialog、Table、検索結果State等を追加しない。</x:v>
+        <x:v>実在するComponentとStateだけを記載する。State IDはSTATE-001から採番し、06 Event／07 API／09テストと連結する。適用する基本設計の初期値・保持・破棄・表示条件を具体化し、File／Sheet／ID又はCell位置を根拠として記す。</x:v>
       </x:c>
       <x:c r="B5" s="59"/>
       <x:c r="C5" s="59"/>
@@ -8925,376 +8941,398 @@
         <x:v>No.</x:v>
       </x:c>
       <x:c r="B20" s="76" t="str">
+        <x:v>State ID</x:v>
+      </x:c>
+      <x:c r="C20" s="76" t="str">
         <x:v>State／Form項目</x:v>
       </x:c>
-      <x:c r="C20" s="76" t="str">
+      <x:c r="D20" s="76" t="str">
         <x:v>管理区分</x:v>
       </x:c>
-      <x:c r="D20" s="76" t="str">
+      <x:c r="E20" s="76" t="str">
         <x:v>管理場所</x:v>
       </x:c>
-      <x:c r="E20" s="76" t="str">
+      <x:c r="F20" s="76" t="str">
         <x:v>Type</x:v>
       </x:c>
-      <x:c r="F20" s="76" t="str">
+      <x:c r="G20" s="76" t="str">
         <x:v>初期値</x:v>
       </x:c>
-      <x:c r="G20" s="76" t="str">
+      <x:c r="H20" s="76" t="str">
         <x:v>更新Event／タイミング</x:v>
       </x:c>
-      <x:c r="H20" s="76" t="str">
+      <x:c r="I20" s="76" t="str">
         <x:v>用途</x:v>
       </x:c>
-      <x:c r="I20" s="76" t="str">
+      <x:c r="J20" s="76" t="str">
         <x:v>保持／破棄条件</x:v>
       </x:c>
-      <x:c r="J20" s="76" t="str">
+      <x:c r="K20" s="76" t="str">
         <x:v>関連ITEM／API</x:v>
       </x:c>
-      <x:c r="K20" s="76" t="str">
+      <x:c r="L20" s="76" t="str">
         <x:v>備考</x:v>
       </x:c>
-      <x:c r="L20" s="2"/>
     </x:row>
     <x:row r="21" ht="36" hidden="0" customHeight="1">
       <x:c r="A21" s="79" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="B21" s="81" t="str">
+        <x:v>STATE-001</x:v>
+      </x:c>
+      <x:c r="C21" s="81" t="str">
         <x:v>&lt;&lt;名称&gt;&gt;</x:v>
       </x:c>
-      <x:c r="C21" s="81" t="str">
+      <x:c r="D21" s="81" t="str">
         <x:v>&lt;&lt;Form State／Local State／Global State／URL State&gt;&gt;</x:v>
       </x:c>
-      <x:c r="D21" s="81" t="str">
+      <x:c r="E21" s="81" t="str">
         <x:v>&lt;&lt;Form／Component／Store／URL&gt;&gt;</x:v>
       </x:c>
-      <x:c r="E21" s="81" t="str">
+      <x:c r="F21" s="81" t="str">
         <x:v>&lt;&lt;型&gt;&gt;</x:v>
       </x:c>
-      <x:c r="F21" s="81" t="str">
+      <x:c r="G21" s="81" t="str">
         <x:v>&lt;&lt;値&gt;&gt;</x:v>
       </x:c>
-      <x:c r="G21" s="81" t="str">
+      <x:c r="H21" s="81" t="str">
         <x:v>&lt;&lt;EVT／API結果&gt;&gt;</x:v>
       </x:c>
-      <x:c r="H21" s="81" t="str">
+      <x:c r="I21" s="81" t="str">
         <x:v>&lt;&lt;表示・制御・送信等&gt;&gt;</x:v>
       </x:c>
-      <x:c r="I21" s="81" t="str">
+      <x:c r="J21" s="81" t="str">
         <x:v>&lt;&lt;遷移、再表示時&gt;&gt;</x:v>
       </x:c>
-      <x:c r="J21" s="81" t="str">
+      <x:c r="K21" s="81" t="str">
         <x:v>&lt;&lt;ID&gt;&gt;</x:v>
       </x:c>
-      <x:c r="K21" s="81" t="str"/>
-      <x:c r="L21" s="2"/>
+      <x:c r="L21" s="81"/>
     </x:row>
     <x:row r="22" ht="36" hidden="0" customHeight="1">
       <x:c r="A22" s="80" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B22" s="81" t="str">
+        <x:v>STATE-002</x:v>
+      </x:c>
+      <x:c r="C22" s="81" t="str">
         <x:v>&lt;&lt;名称&gt;&gt;</x:v>
       </x:c>
-      <x:c r="C22" s="81" t="str">
+      <x:c r="D22" s="81" t="str">
         <x:v>&lt;&lt;Form State／Local State／Global State／URL State&gt;&gt;</x:v>
       </x:c>
-      <x:c r="D22" s="81" t="str">
+      <x:c r="E22" s="81" t="str">
         <x:v>&lt;&lt;Form／Component／Store／URL&gt;&gt;</x:v>
       </x:c>
-      <x:c r="E22" s="81" t="str">
+      <x:c r="F22" s="81" t="str">
         <x:v>&lt;&lt;型&gt;&gt;</x:v>
       </x:c>
-      <x:c r="F22" s="81" t="str">
+      <x:c r="G22" s="81" t="str">
         <x:v>&lt;&lt;値&gt;&gt;</x:v>
       </x:c>
-      <x:c r="G22" s="81" t="str">
+      <x:c r="H22" s="81" t="str">
         <x:v>&lt;&lt;EVT／API結果&gt;&gt;</x:v>
       </x:c>
-      <x:c r="H22" s="81" t="str">
+      <x:c r="I22" s="81" t="str">
         <x:v>&lt;&lt;表示・制御・送信等&gt;&gt;</x:v>
       </x:c>
-      <x:c r="I22" s="81" t="str">
+      <x:c r="J22" s="81" t="str">
         <x:v>&lt;&lt;遷移、再表示時&gt;&gt;</x:v>
       </x:c>
-      <x:c r="J22" s="81" t="str">
+      <x:c r="K22" s="81" t="str">
         <x:v>&lt;&lt;ID&gt;&gt;</x:v>
       </x:c>
-      <x:c r="K22" s="81" t="str"/>
-      <x:c r="L22" s="2"/>
+      <x:c r="L22" s="81"/>
     </x:row>
     <x:row r="23" ht="36" hidden="0" customHeight="1">
       <x:c r="A23" s="79" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="B23" s="81" t="str">
+        <x:v>STATE-003</x:v>
+      </x:c>
+      <x:c r="C23" s="81" t="str">
         <x:v>&lt;&lt;名称&gt;&gt;</x:v>
       </x:c>
-      <x:c r="C23" s="81" t="str">
+      <x:c r="D23" s="81" t="str">
         <x:v>&lt;&lt;Form State／Local State／Global State／URL State&gt;&gt;</x:v>
       </x:c>
-      <x:c r="D23" s="81" t="str">
+      <x:c r="E23" s="81" t="str">
         <x:v>&lt;&lt;Form／Component／Store／URL&gt;&gt;</x:v>
       </x:c>
-      <x:c r="E23" s="81" t="str">
+      <x:c r="F23" s="81" t="str">
         <x:v>&lt;&lt;型&gt;&gt;</x:v>
       </x:c>
-      <x:c r="F23" s="81" t="str">
+      <x:c r="G23" s="81" t="str">
         <x:v>&lt;&lt;値&gt;&gt;</x:v>
       </x:c>
-      <x:c r="G23" s="81" t="str">
+      <x:c r="H23" s="81" t="str">
         <x:v>&lt;&lt;EVT／API結果&gt;&gt;</x:v>
       </x:c>
-      <x:c r="H23" s="81" t="str">
+      <x:c r="I23" s="81" t="str">
         <x:v>&lt;&lt;表示・制御・送信等&gt;&gt;</x:v>
       </x:c>
-      <x:c r="I23" s="81" t="str">
+      <x:c r="J23" s="81" t="str">
         <x:v>&lt;&lt;遷移、再表示時&gt;&gt;</x:v>
       </x:c>
-      <x:c r="J23" s="81" t="str">
+      <x:c r="K23" s="81" t="str">
         <x:v>&lt;&lt;ID&gt;&gt;</x:v>
       </x:c>
-      <x:c r="K23" s="81" t="str"/>
-      <x:c r="L23" s="2"/>
+      <x:c r="L23" s="81"/>
     </x:row>
     <x:row r="24" ht="36" hidden="0" customHeight="1">
       <x:c r="A24" s="80" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="B24" s="81" t="str">
+        <x:v>STATE-004</x:v>
+      </x:c>
+      <x:c r="C24" s="81" t="str">
         <x:v>&lt;&lt;名称&gt;&gt;</x:v>
       </x:c>
-      <x:c r="C24" s="81" t="str">
+      <x:c r="D24" s="81" t="str">
         <x:v>&lt;&lt;Form State／Local State／Global State／URL State&gt;&gt;</x:v>
       </x:c>
-      <x:c r="D24" s="81" t="str">
+      <x:c r="E24" s="81" t="str">
         <x:v>&lt;&lt;Form／Component／Store／URL&gt;&gt;</x:v>
       </x:c>
-      <x:c r="E24" s="81" t="str">
+      <x:c r="F24" s="81" t="str">
         <x:v>&lt;&lt;型&gt;&gt;</x:v>
       </x:c>
-      <x:c r="F24" s="81" t="str">
+      <x:c r="G24" s="81" t="str">
         <x:v>&lt;&lt;値&gt;&gt;</x:v>
       </x:c>
-      <x:c r="G24" s="81" t="str">
+      <x:c r="H24" s="81" t="str">
         <x:v>&lt;&lt;EVT／API結果&gt;&gt;</x:v>
       </x:c>
-      <x:c r="H24" s="81" t="str">
+      <x:c r="I24" s="81" t="str">
         <x:v>&lt;&lt;表示・制御・送信等&gt;&gt;</x:v>
       </x:c>
-      <x:c r="I24" s="81" t="str">
+      <x:c r="J24" s="81" t="str">
         <x:v>&lt;&lt;遷移、再表示時&gt;&gt;</x:v>
       </x:c>
-      <x:c r="J24" s="81" t="str">
+      <x:c r="K24" s="81" t="str">
         <x:v>&lt;&lt;ID&gt;&gt;</x:v>
       </x:c>
-      <x:c r="K24" s="81" t="str"/>
-      <x:c r="L24" s="2"/>
+      <x:c r="L24" s="81"/>
     </x:row>
     <x:row r="25" ht="36" hidden="0" customHeight="1">
       <x:c r="A25" s="79" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="B25" s="81" t="str">
+        <x:v>STATE-005</x:v>
+      </x:c>
+      <x:c r="C25" s="81" t="str">
         <x:v>&lt;&lt;名称&gt;&gt;</x:v>
       </x:c>
-      <x:c r="C25" s="81" t="str">
+      <x:c r="D25" s="81" t="str">
         <x:v>&lt;&lt;Form State／Local State／Global State／URL State&gt;&gt;</x:v>
       </x:c>
-      <x:c r="D25" s="81" t="str">
+      <x:c r="E25" s="81" t="str">
         <x:v>&lt;&lt;Form／Component／Store／URL&gt;&gt;</x:v>
       </x:c>
-      <x:c r="E25" s="81" t="str">
+      <x:c r="F25" s="81" t="str">
         <x:v>&lt;&lt;型&gt;&gt;</x:v>
       </x:c>
-      <x:c r="F25" s="81" t="str">
+      <x:c r="G25" s="81" t="str">
         <x:v>&lt;&lt;値&gt;&gt;</x:v>
       </x:c>
-      <x:c r="G25" s="81" t="str">
+      <x:c r="H25" s="81" t="str">
         <x:v>&lt;&lt;EVT／API結果&gt;&gt;</x:v>
       </x:c>
-      <x:c r="H25" s="81" t="str">
+      <x:c r="I25" s="81" t="str">
         <x:v>&lt;&lt;表示・制御・送信等&gt;&gt;</x:v>
       </x:c>
-      <x:c r="I25" s="81" t="str">
+      <x:c r="J25" s="81" t="str">
         <x:v>&lt;&lt;遷移、再表示時&gt;&gt;</x:v>
       </x:c>
-      <x:c r="J25" s="81" t="str">
+      <x:c r="K25" s="81" t="str">
         <x:v>&lt;&lt;ID&gt;&gt;</x:v>
       </x:c>
-      <x:c r="K25" s="81" t="str"/>
-      <x:c r="L25" s="2"/>
+      <x:c r="L25" s="81"/>
     </x:row>
     <x:row r="26" ht="36" hidden="0" customHeight="1">
       <x:c r="A26" s="80" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="B26" s="81" t="str">
+        <x:v>STATE-006</x:v>
+      </x:c>
+      <x:c r="C26" s="81" t="str">
         <x:v>&lt;&lt;名称&gt;&gt;</x:v>
       </x:c>
-      <x:c r="C26" s="81" t="str">
+      <x:c r="D26" s="81" t="str">
         <x:v>&lt;&lt;Form State／Local State／Global State／URL State&gt;&gt;</x:v>
       </x:c>
-      <x:c r="D26" s="81" t="str">
+      <x:c r="E26" s="81" t="str">
         <x:v>&lt;&lt;Form／Component／Store／URL&gt;&gt;</x:v>
       </x:c>
-      <x:c r="E26" s="81" t="str">
+      <x:c r="F26" s="81" t="str">
         <x:v>&lt;&lt;型&gt;&gt;</x:v>
       </x:c>
-      <x:c r="F26" s="81" t="str">
+      <x:c r="G26" s="81" t="str">
         <x:v>&lt;&lt;値&gt;&gt;</x:v>
       </x:c>
-      <x:c r="G26" s="81" t="str">
+      <x:c r="H26" s="81" t="str">
         <x:v>&lt;&lt;EVT／API結果&gt;&gt;</x:v>
       </x:c>
-      <x:c r="H26" s="81" t="str">
+      <x:c r="I26" s="81" t="str">
         <x:v>&lt;&lt;表示・制御・送信等&gt;&gt;</x:v>
       </x:c>
-      <x:c r="I26" s="81" t="str">
+      <x:c r="J26" s="81" t="str">
         <x:v>&lt;&lt;遷移、再表示時&gt;&gt;</x:v>
       </x:c>
-      <x:c r="J26" s="81" t="str">
+      <x:c r="K26" s="81" t="str">
         <x:v>&lt;&lt;ID&gt;&gt;</x:v>
       </x:c>
-      <x:c r="K26" s="81" t="str"/>
-      <x:c r="L26" s="2"/>
+      <x:c r="L26" s="81"/>
     </x:row>
     <x:row r="27" ht="36" hidden="0" customHeight="1">
       <x:c r="A27" s="79" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="B27" s="81" t="str">
+        <x:v>STATE-007</x:v>
+      </x:c>
+      <x:c r="C27" s="81" t="str">
         <x:v>&lt;&lt;名称&gt;&gt;</x:v>
       </x:c>
-      <x:c r="C27" s="81" t="str">
+      <x:c r="D27" s="81" t="str">
         <x:v>&lt;&lt;Form State／Local State／Global State／URL State&gt;&gt;</x:v>
       </x:c>
-      <x:c r="D27" s="81" t="str">
+      <x:c r="E27" s="81" t="str">
         <x:v>&lt;&lt;Form／Component／Store／URL&gt;&gt;</x:v>
       </x:c>
-      <x:c r="E27" s="81" t="str">
+      <x:c r="F27" s="81" t="str">
         <x:v>&lt;&lt;型&gt;&gt;</x:v>
       </x:c>
-      <x:c r="F27" s="81" t="str">
+      <x:c r="G27" s="81" t="str">
         <x:v>&lt;&lt;値&gt;&gt;</x:v>
       </x:c>
-      <x:c r="G27" s="81" t="str">
+      <x:c r="H27" s="81" t="str">
         <x:v>&lt;&lt;EVT／API結果&gt;&gt;</x:v>
       </x:c>
-      <x:c r="H27" s="81" t="str">
+      <x:c r="I27" s="81" t="str">
         <x:v>&lt;&lt;表示・制御・送信等&gt;&gt;</x:v>
       </x:c>
-      <x:c r="I27" s="81" t="str">
+      <x:c r="J27" s="81" t="str">
         <x:v>&lt;&lt;遷移、再表示時&gt;&gt;</x:v>
       </x:c>
-      <x:c r="J27" s="81" t="str">
+      <x:c r="K27" s="81" t="str">
         <x:v>&lt;&lt;ID&gt;&gt;</x:v>
       </x:c>
-      <x:c r="K27" s="81" t="str"/>
-      <x:c r="L27" s="2"/>
+      <x:c r="L27" s="81"/>
     </x:row>
     <x:row r="28" ht="36" hidden="0" customHeight="1">
       <x:c r="A28" s="80" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="B28" s="81" t="str">
+        <x:v>STATE-008</x:v>
+      </x:c>
+      <x:c r="C28" s="81" t="str">
         <x:v>&lt;&lt;名称&gt;&gt;</x:v>
       </x:c>
-      <x:c r="C28" s="81" t="str">
+      <x:c r="D28" s="81" t="str">
         <x:v>&lt;&lt;Form State／Local State／Global State／URL State&gt;&gt;</x:v>
       </x:c>
-      <x:c r="D28" s="81" t="str">
+      <x:c r="E28" s="81" t="str">
         <x:v>&lt;&lt;Form／Component／Store／URL&gt;&gt;</x:v>
       </x:c>
-      <x:c r="E28" s="81" t="str">
+      <x:c r="F28" s="81" t="str">
         <x:v>&lt;&lt;型&gt;&gt;</x:v>
       </x:c>
-      <x:c r="F28" s="81" t="str">
+      <x:c r="G28" s="81" t="str">
         <x:v>&lt;&lt;値&gt;&gt;</x:v>
       </x:c>
-      <x:c r="G28" s="81" t="str">
+      <x:c r="H28" s="81" t="str">
         <x:v>&lt;&lt;EVT／API結果&gt;&gt;</x:v>
       </x:c>
-      <x:c r="H28" s="81" t="str">
+      <x:c r="I28" s="81" t="str">
         <x:v>&lt;&lt;表示・制御・送信等&gt;&gt;</x:v>
       </x:c>
-      <x:c r="I28" s="81" t="str">
+      <x:c r="J28" s="81" t="str">
         <x:v>&lt;&lt;遷移、再表示時&gt;&gt;</x:v>
       </x:c>
-      <x:c r="J28" s="81" t="str">
+      <x:c r="K28" s="81" t="str">
         <x:v>&lt;&lt;ID&gt;&gt;</x:v>
       </x:c>
-      <x:c r="K28" s="81" t="str"/>
-      <x:c r="L28" s="2"/>
+      <x:c r="L28" s="81"/>
     </x:row>
     <x:row r="29" ht="36" hidden="0" customHeight="1">
       <x:c r="A29" s="79" t="n">
         <x:v>9</x:v>
       </x:c>
       <x:c r="B29" s="81" t="str">
+        <x:v>STATE-009</x:v>
+      </x:c>
+      <x:c r="C29" s="81" t="str">
         <x:v>&lt;&lt;名称&gt;&gt;</x:v>
       </x:c>
-      <x:c r="C29" s="81" t="str">
+      <x:c r="D29" s="81" t="str">
         <x:v>&lt;&lt;Form State／Local State／Global State／URL State&gt;&gt;</x:v>
       </x:c>
-      <x:c r="D29" s="81" t="str">
+      <x:c r="E29" s="81" t="str">
         <x:v>&lt;&lt;Form／Component／Store／URL&gt;&gt;</x:v>
       </x:c>
-      <x:c r="E29" s="81" t="str">
+      <x:c r="F29" s="81" t="str">
         <x:v>&lt;&lt;型&gt;&gt;</x:v>
       </x:c>
-      <x:c r="F29" s="81" t="str">
+      <x:c r="G29" s="81" t="str">
         <x:v>&lt;&lt;値&gt;&gt;</x:v>
       </x:c>
-      <x:c r="G29" s="81" t="str">
+      <x:c r="H29" s="81" t="str">
         <x:v>&lt;&lt;EVT／API結果&gt;&gt;</x:v>
       </x:c>
-      <x:c r="H29" s="81" t="str">
+      <x:c r="I29" s="81" t="str">
         <x:v>&lt;&lt;表示・制御・送信等&gt;&gt;</x:v>
       </x:c>
-      <x:c r="I29" s="81" t="str">
+      <x:c r="J29" s="81" t="str">
         <x:v>&lt;&lt;遷移、再表示時&gt;&gt;</x:v>
       </x:c>
-      <x:c r="J29" s="81" t="str">
+      <x:c r="K29" s="81" t="str">
         <x:v>&lt;&lt;ID&gt;&gt;</x:v>
       </x:c>
-      <x:c r="K29" s="81" t="str"/>
-      <x:c r="L29" s="2"/>
+      <x:c r="L29" s="81"/>
     </x:row>
     <x:row r="30" ht="36" hidden="0" customHeight="1">
       <x:c r="A30" s="80" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="B30" s="81" t="str">
+        <x:v>STATE-010</x:v>
+      </x:c>
+      <x:c r="C30" s="81" t="str">
         <x:v>&lt;&lt;名称&gt;&gt;</x:v>
       </x:c>
-      <x:c r="C30" s="81" t="str">
+      <x:c r="D30" s="81" t="str">
         <x:v>&lt;&lt;Form State／Local State／Global State／URL State&gt;&gt;</x:v>
       </x:c>
-      <x:c r="D30" s="81" t="str">
+      <x:c r="E30" s="81" t="str">
         <x:v>&lt;&lt;Form／Component／Store／URL&gt;&gt;</x:v>
       </x:c>
-      <x:c r="E30" s="81" t="str">
+      <x:c r="F30" s="81" t="str">
         <x:v>&lt;&lt;型&gt;&gt;</x:v>
       </x:c>
-      <x:c r="F30" s="81" t="str">
+      <x:c r="G30" s="81" t="str">
         <x:v>&lt;&lt;値&gt;&gt;</x:v>
       </x:c>
-      <x:c r="G30" s="81" t="str">
+      <x:c r="H30" s="81" t="str">
         <x:v>&lt;&lt;EVT／API結果&gt;&gt;</x:v>
       </x:c>
-      <x:c r="H30" s="81" t="str">
+      <x:c r="I30" s="81" t="str">
         <x:v>&lt;&lt;表示・制御・送信等&gt;&gt;</x:v>
       </x:c>
-      <x:c r="I30" s="81" t="str">
+      <x:c r="J30" s="81" t="str">
         <x:v>&lt;&lt;遷移、再表示時&gt;&gt;</x:v>
       </x:c>
-      <x:c r="J30" s="81" t="str">
+      <x:c r="K30" s="81" t="str">
         <x:v>&lt;&lt;ID&gt;&gt;</x:v>
       </x:c>
-      <x:c r="K30" s="81" t="str"/>
-      <x:c r="L30" s="2"/>
+      <x:c r="L30" s="81"/>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="2"/>
@@ -10133,7 +10171,7 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="J2" s="69" t="str">
-        <x:v>Ver.2.2</x:v>
+        <x:v>Ver.2.3</x:v>
       </x:c>
       <x:c r="K2" s="69"/>
       <x:c r="L2" s="69"/>
@@ -12356,7 +12394,7 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="J2" s="69" t="str">
-        <x:v>Ver.2.2</x:v>
+        <x:v>Ver.2.3</x:v>
       </x:c>
       <x:c r="K2" s="69"/>
       <x:c r="L2" s="69"/>
@@ -14730,7 +14768,7 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="J2" s="69" t="str">
-        <x:v>Ver.2.2</x:v>
+        <x:v>Ver.2.3</x:v>
       </x:c>
       <x:c r="K2" s="69"/>
       <x:c r="L2" s="69"/>
